--- a/diseases/d234/1995-1999.xlsx
+++ b/diseases/d234/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>2</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>2</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>3</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>2</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>2</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>1</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>3</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>2</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>2</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>1</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>2</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>2</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14520,9 +14415,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14913,9 +14805,6 @@
       <c r="O74" t="n">
         <v>3</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15306,9 +15195,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15699,9 +15585,6 @@
       <c r="O78" t="n">
         <v>3</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16092,9 +15975,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16485,9 +16365,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16878,9 +16755,6 @@
       <c r="O84" t="n">
         <v>2</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17271,9 +17145,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17664,9 +17535,6 @@
       <c r="O88" t="n">
         <v>2</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18057,9 +17925,6 @@
       <c r="O90" t="n">
         <v>1</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18450,9 +18315,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19002,9 +18864,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="S95" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19395,9 +19254,6 @@
       <c r="O97" t="n">
         <v>1</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="S97" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19947,9 +19803,6 @@
       <c r="O100" t="n">
         <v>1</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="S100" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20340,9 +20193,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="S102" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20892,9 +20742,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="S105" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21285,9 +21132,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="S107" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21837,9 +21681,6 @@
       <c r="O110" t="n">
         <v>5</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="S110" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22230,9 +22071,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="S112" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22782,9 +22620,6 @@
       <c r="O115" t="n">
         <v>2</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="S115" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23175,9 +23010,6 @@
       <c r="O117" t="n">
         <v>1</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="S117" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23727,9 +23559,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="S120" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24120,9 +23949,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="S122" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24672,9 +24498,6 @@
       <c r="O125" t="n">
         <v>2</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="S125" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25065,9 +24888,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="S127" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25617,9 +25437,6 @@
       <c r="O130" t="n">
         <v>2</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="S130" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26010,9 +25827,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="S132" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26562,9 +26376,6 @@
       <c r="O135" t="n">
         <v>4</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="S135" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26955,9 +26766,6 @@
       <c r="O137" t="n">
         <v>1</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="S137" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27507,9 +27315,6 @@
       <c r="O140" t="n">
         <v>3</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="S140" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27900,9 +27705,6 @@
       <c r="O142" t="n">
         <v>1</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="S142" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28452,9 +28254,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="S145" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28845,9 +28644,6 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="S147" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29397,9 +29193,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="S150" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29790,9 +29583,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="S152" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30342,9 +30132,6 @@
       <c r="O155" t="n">
         <v>2</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="S155" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30735,9 +30522,6 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="S157" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31287,9 +31071,6 @@
       <c r="O160" t="n">
         <v>2</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="S160" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31680,9 +31461,6 @@
       <c r="O162" t="n">
         <v>1</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="S162" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32232,9 +32010,6 @@
       <c r="O165" t="n">
         <v>2</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="S165" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32625,9 +32400,6 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="S167" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33177,9 +32949,6 @@
       <c r="O170" t="n">
         <v>3</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="S170" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33570,9 +33339,6 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="S172" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34122,9 +33888,6 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="S175" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34515,9 +34278,6 @@
       <c r="O177" t="n">
         <v>1</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="S177" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35067,9 +34827,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="S180" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35460,9 +35217,6 @@
       <c r="O182" t="n">
         <v>1</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="S182" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36012,9 +35766,6 @@
       <c r="O185" t="n">
         <v>2</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="S185" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36405,9 +36156,6 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="S187" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36957,9 +36705,6 @@
       <c r="O190" t="n">
         <v>3</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="S190" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37350,9 +37095,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="S192" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37902,9 +37644,6 @@
       <c r="O195" t="n">
         <v>2</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="S195" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38295,9 +38034,6 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="S197" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38847,9 +38583,6 @@
       <c r="O200" t="n">
         <v>2</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="S200" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39240,9 +38973,6 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="S202" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39792,9 +39522,6 @@
       <c r="O205" t="n">
         <v>2</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="S205" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40185,9 +39912,6 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="S207" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40737,9 +40461,6 @@
       <c r="O210" t="n">
         <v>1</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="S210" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41130,9 +40851,6 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="S212" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41682,9 +41400,6 @@
       <c r="O215" t="n">
         <v>4</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="S215" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42075,9 +41790,6 @@
       <c r="O217" t="n">
         <v>0</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="S217" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42627,9 +42339,6 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="S220" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43020,9 +42729,6 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="S222" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43572,9 +43278,6 @@
       <c r="O225" t="n">
         <v>2</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="S225" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43965,9 +43668,6 @@
       <c r="O227" t="n">
         <v>0</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="S227" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44517,9 +44217,6 @@
       <c r="O230" t="n">
         <v>0</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="S230" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44910,9 +44607,6 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="S232" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45462,9 +45156,6 @@
       <c r="O235" t="n">
         <v>2</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="S235" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45855,9 +45546,6 @@
       <c r="O237" t="n">
         <v>0</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="S237" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46407,9 +46095,6 @@
       <c r="O240" t="n">
         <v>1</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="S240" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46800,9 +46485,6 @@
       <c r="O242" t="n">
         <v>1</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="S242" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47352,9 +47034,6 @@
       <c r="O245" t="n">
         <v>1</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="S245" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47745,9 +47424,6 @@
       <c r="O247" t="n">
         <v>29</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="S247" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48297,9 +47973,6 @@
       <c r="O250" t="n">
         <v>32</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="S250" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48690,9 +48363,6 @@
       <c r="O252" t="n">
         <v>4</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="S252" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49242,9 +48912,6 @@
       <c r="O255" t="n">
         <v>39</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="S255" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49635,9 +49302,6 @@
       <c r="O257" t="n">
         <v>0</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="S257" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50187,9 +49851,6 @@
       <c r="O260" t="n">
         <v>2</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="S260" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50580,9 +50241,6 @@
       <c r="O262" t="n">
         <v>1</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="S262" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51132,9 +50790,6 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="S265" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51525,9 +51180,6 @@
       <c r="O267" t="n">
         <v>0</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="S267" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -52076,9 +51728,6 @@
       </c>
       <c r="O270" t="n">
         <v>1</v>
-      </c>
-      <c r="Q270" t="n">
-        <v>0</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
